--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/abr-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.351.814-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -819,7 +831,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057931-1-CM25</t>
+          <t>4642-2153-SE25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +846,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,43 +856,47 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>60.514.000-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>6896.54</v>
+        <v>6418.79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057931-2-CM25</t>
+          <t>598-59-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,27 +921,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>61.513.000-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>MUEBLES EASTON LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>79.526.830-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +951,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6896.54</v>
+        <v>41132.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1208066-97-CM25</t>
+          <t>2859-221-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -961,42 +977,46 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7001.98</v>
+        <v>13631.01</v>
       </c>
     </row>
     <row r="10">
@@ -1063,7 +1083,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2859-221-CM25</t>
+          <t>1208066-97-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,48 +1103,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>13631.01</v>
+        <v>7001.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>598-59-CM25</t>
+          <t>1057931-2-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,43 +1173,47 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.513.000-1</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>DIRECCION PREVISION DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MUEBLES EASTON LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.526.830-8</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>41132.27</v>
+        <v>6896.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>867990-337-CM25</t>
+          <t>1057931-1-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1228,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,43 +1238,47 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>TAZ S A</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.891.420-0</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6856.81</v>
+        <v>6896.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1320310-14-CM25</t>
+          <t>867990-337-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1293,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1303,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1318,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>INTERGROUPE S.A.</t>
+          <t>TAZ S A</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.719.470-6</t>
+          <t>96.891.420-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1333,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>14687.81</v>
+        <v>6856.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>628-91-CM25</t>
+          <t>1320310-14-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1332,27 +1364,27 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>INTERGROUPE S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>76.719.470-6</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1394,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13428.09</v>
+        <v>14687.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5890-36-CM25</t>
+          <t>628-91-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1415,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,43 +1425,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7578.17</v>
+        <v>13428.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>652-127-CM25</t>
+          <t>5890-36-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1454,27 +1490,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.954.500-1</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.559.762-5</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1520,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5564.64</v>
+        <v>7578.17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>622-200-CM25</t>
+          <t>652-127-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1515,43 +1551,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>61.954.500-1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>SERVICIO DE SALUD ARAUCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>COMERCIALIZADORA MERCADO PUBLICO SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>76.559.762-5</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>18603.93</v>
+        <v>5564.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-658-CM25</t>
+          <t>622-200-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1576,27 +1616,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1646,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5564.65</v>
+        <v>18603.93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5703-8-CM25</t>
+          <t>2026-658-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1667,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,27 +1677,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>OFISILLAS CHILE SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.855.435-8</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1707,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>28292.51</v>
+        <v>5564.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3453-164-CM25</t>
+          <t>5703-8-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,43 +1738,47 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+          <t>76.855.435-8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>20231.52</v>
+        <v>28292.51</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2324-533-CM25</t>
+          <t>3453-164-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,32 +1798,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1833,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>26749.32</v>
+        <v>20231.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1057536-2100-CM25</t>
+          <t>2324-533-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1815,17 +1859,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,28 +1879,32 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIAL VYB SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.583.479-1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>12583.78</v>
+        <v>26749.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1208066-112-CM25</t>
+          <t>1057536-2100-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,32 +1924,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>COMERCIAL VYB SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.583.479-1</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1959,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8444.639999999999</v>
+        <v>12583.78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1375753-16-CM25</t>
+          <t>1208066-112-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,53 +1980,57 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.981.290-5</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.235.755-0</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>9236.040000000001</v>
+        <v>8444.639999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057536-2102-CM25</t>
+          <t>1375753-16-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +2045,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,27 +2055,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.700-7</t>
+          <t>61.981.290-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>FABRICACION Y ARMADO DE SILLAS HECTOR HERNANDEZ EIRL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.235.755-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2085,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8943.030000000001</v>
+        <v>9236.040000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-694-CM25</t>
+          <t>1079650-11-SE25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,53 +2106,57 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>61.607.100-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>ALQUEZAR SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>77.714.556-8</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7515.47</v>
+        <v>8844.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-680-CM25</t>
+          <t>1057536-2102-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2171,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,43 +2181,47 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>61.607.700-7</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JUEGOS MAGICOS</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.102.918-5</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>77.599.784-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6935.48</v>
+        <v>8943.030000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-693-CM25</t>
+          <t>2026-694-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2201,28 +2261,32 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.616.370-6</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>77.346.435-9</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>10231.99</v>
+        <v>7515.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4146-16-CM25</t>
+          <t>2026-680-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2301,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,27 +2311,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.505.000-K</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>JUEGOS MAGICOS</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.102.918-5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,6 +2341,136 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
+        <v>6935.48</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-693-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.606.600-5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MADERERA LAGO VILLARRICA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>78.616.370-6</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>10231.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4146-16-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-3-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>60.505.000-K</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>MELMAN SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
         <v>12584.81</v>
       </c>
     </row>
